--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487998_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487998_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>8.7674</v>
+        <v>6.2018</v>
       </c>
       <c r="E2" t="n">
-        <v>9.2935</v>
+        <v>7.1772</v>
       </c>
       <c r="F2" t="n">
-        <v>-0.5262</v>
+        <v>-0.9754</v>
       </c>
       <c r="G2" t="n">
         <v>1.5544</v>
@@ -610,13 +610,13 @@
         <v>3.568</v>
       </c>
       <c r="S2" t="n">
-        <v>3.1878</v>
+        <v>0.6222</v>
       </c>
       <c r="T2" t="n">
-        <v>3.4546</v>
+        <v>1.3383</v>
       </c>
       <c r="U2" t="n">
-        <v>-0.2668</v>
+        <v>-0.716</v>
       </c>
       <c r="V2" t="n">
         <v>2.4394</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>2.0571</v>
+        <v>3.2068</v>
       </c>
       <c r="E3" t="n">
-        <v>3.3899</v>
+        <v>4.5958</v>
       </c>
       <c r="F3" t="n">
-        <v>-1.3329</v>
+        <v>-1.389</v>
       </c>
       <c r="G3" t="n">
         <v>-1.0374</v>
@@ -688,13 +688,13 @@
         <v>2.9733</v>
       </c>
       <c r="S3" t="n">
-        <v>-1.4984</v>
+        <v>-0.3487</v>
       </c>
       <c r="T3" t="n">
-        <v>-1.0387</v>
+        <v>0.1672</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.4597</v>
+        <v>-0.5159</v>
       </c>
       <c r="V3" t="n">
         <v>1.6195</v>
@@ -721,13 +721,13 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>1.0605</v>
+        <v>2.4567</v>
       </c>
       <c r="E4" t="n">
-        <v>1.0466</v>
+        <v>2.1901</v>
       </c>
       <c r="F4" t="n">
-        <v>0.0139</v>
+        <v>0.2666</v>
       </c>
       <c r="G4" t="n">
         <v>-0.6451</v>
@@ -766,13 +766,13 @@
         <v>2.9733</v>
       </c>
       <c r="S4" t="n">
-        <v>-1.821</v>
+        <v>-0.4248</v>
       </c>
       <c r="T4" t="n">
-        <v>-1.0387</v>
+        <v>0.1048</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.7823</v>
+        <v>-0.5296</v>
       </c>
       <c r="V4" t="n">
         <v>0.5532</v>
@@ -799,13 +799,13 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>-0.2725</v>
+        <v>-0.2444</v>
       </c>
       <c r="E5" t="n">
         <v>-0.2235</v>
       </c>
       <c r="F5" t="n">
-        <v>-0.049</v>
+        <v>-0.0209</v>
       </c>
       <c r="G5" t="n">
         <v>-0.3022</v>
@@ -844,13 +844,13 @@
         <v>0.1982</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.1685</v>
+        <v>-0.1404</v>
       </c>
       <c r="T5" t="n">
         <v>-0.1872</v>
       </c>
       <c r="U5" t="n">
-        <v>0.0187</v>
+        <v>0.0468</v>
       </c>
       <c r="V5" t="n">
         <v>0</v>
@@ -865,7 +865,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>T. LIBERATORE DARGAM</t>
+          <t>S. CURBELO MENENDEZ</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,73 +877,73 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>-1.7106</v>
+        <v>-1.3561</v>
       </c>
       <c r="E6" t="n">
-        <v>-0.6405</v>
+        <v>0.3848</v>
       </c>
       <c r="F6" t="n">
-        <v>-1.0701</v>
+        <v>-1.7408</v>
       </c>
       <c r="G6" t="n">
-        <v>-0.4118</v>
+        <v>-1.8304</v>
       </c>
       <c r="H6" t="n">
-        <v>-1.7338</v>
+        <v>-3.8603</v>
       </c>
       <c r="I6" t="n">
-        <v>1.322</v>
+        <v>2.0299</v>
       </c>
       <c r="J6" t="n">
-        <v>0.1083</v>
+        <v>2.0351</v>
       </c>
       <c r="K6" t="n">
-        <v>-1.3381</v>
+        <v>-0.5039</v>
       </c>
       <c r="L6" t="n">
-        <v>1.4464</v>
+        <v>2.539</v>
       </c>
       <c r="M6" t="n">
-        <v>-0.5201</v>
+        <v>-3.8655</v>
       </c>
       <c r="N6" t="n">
-        <v>-0.3957</v>
+        <v>-3.3564</v>
       </c>
       <c r="O6" t="n">
-        <v>-0.1244</v>
+        <v>-0.5091</v>
       </c>
       <c r="P6" t="n">
-        <v>1.784</v>
+        <v>-0.1982</v>
       </c>
       <c r="Q6" t="n">
-        <v>0</v>
+        <v>-1.9822</v>
       </c>
       <c r="R6" t="n">
         <v>1.784</v>
       </c>
       <c r="S6" t="n">
-        <v>-1.6343</v>
+        <v>-0.2679</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.7488</v>
+        <v>0.0653</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.8855</v>
+        <v>-0.3333</v>
       </c>
       <c r="V6" t="n">
-        <v>-1.4485</v>
+        <v>0.9405</v>
       </c>
       <c r="W6" t="n">
-        <v>0</v>
+        <v>0.2666</v>
       </c>
       <c r="X6" t="n">
-        <v>-1.4485</v>
+        <v>0.674</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>J. VICENTE BOSCH</t>
+          <t>T. LIBERATORE DARGAM</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,73 +955,73 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-1.7367</v>
+        <v>-1.3593</v>
       </c>
       <c r="E7" t="n">
-        <v>2.1951</v>
+        <v>-0.233</v>
       </c>
       <c r="F7" t="n">
-        <v>-3.9319</v>
+        <v>-1.1263</v>
       </c>
       <c r="G7" t="n">
-        <v>1.6291</v>
+        <v>-0.4118</v>
       </c>
       <c r="H7" t="n">
-        <v>0.7529</v>
+        <v>-1.7338</v>
       </c>
       <c r="I7" t="n">
-        <v>0.8761</v>
+        <v>1.322</v>
       </c>
       <c r="J7" t="n">
-        <v>4.4796</v>
+        <v>0.1083</v>
       </c>
       <c r="K7" t="n">
-        <v>3.632</v>
+        <v>-1.3381</v>
       </c>
       <c r="L7" t="n">
-        <v>0.8476</v>
+        <v>1.4464</v>
       </c>
       <c r="M7" t="n">
-        <v>-2.8505</v>
+        <v>-0.5201</v>
       </c>
       <c r="N7" t="n">
-        <v>-2.8791</v>
+        <v>-0.3957</v>
       </c>
       <c r="O7" t="n">
-        <v>0.0285</v>
+        <v>-0.1244</v>
       </c>
       <c r="P7" t="n">
-        <v>-1.3876</v>
+        <v>1.784</v>
       </c>
       <c r="Q7" t="n">
-        <v>-2.9733</v>
+        <v>0</v>
       </c>
       <c r="R7" t="n">
-        <v>1.5858</v>
+        <v>1.784</v>
       </c>
       <c r="S7" t="n">
-        <v>-1.0377</v>
+        <v>-1.2829</v>
       </c>
       <c r="T7" t="n">
-        <v>0.4223</v>
+        <v>-0.3413</v>
       </c>
       <c r="U7" t="n">
-        <v>-1.46</v>
+        <v>-0.9416</v>
       </c>
       <c r="V7" t="n">
-        <v>-0.9405</v>
+        <v>-1.4485</v>
       </c>
       <c r="W7" t="n">
-        <v>0.2666</v>
+        <v>0</v>
       </c>
       <c r="X7" t="n">
-        <v>-1.2071</v>
+        <v>-1.4485</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>S. CURBELO MENENDEZ</t>
+          <t>J. VICENTE BOSCH</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,67 +1033,67 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-2.2074</v>
+        <v>-1.5525</v>
       </c>
       <c r="E8" t="n">
-        <v>-0.7193000000000001</v>
+        <v>2.0143</v>
       </c>
       <c r="F8" t="n">
-        <v>-1.4881</v>
+        <v>-3.5668</v>
       </c>
       <c r="G8" t="n">
-        <v>-1.8304</v>
+        <v>1.6291</v>
       </c>
       <c r="H8" t="n">
-        <v>-3.8603</v>
+        <v>0.7529</v>
       </c>
       <c r="I8" t="n">
-        <v>2.0299</v>
+        <v>0.8761</v>
       </c>
       <c r="J8" t="n">
-        <v>2.0351</v>
+        <v>4.4796</v>
       </c>
       <c r="K8" t="n">
-        <v>-0.5039</v>
+        <v>3.632</v>
       </c>
       <c r="L8" t="n">
-        <v>2.539</v>
+        <v>0.8476</v>
       </c>
       <c r="M8" t="n">
-        <v>-3.8655</v>
+        <v>-2.8505</v>
       </c>
       <c r="N8" t="n">
-        <v>-3.3564</v>
+        <v>-2.8791</v>
       </c>
       <c r="O8" t="n">
-        <v>-0.5091</v>
+        <v>0.0285</v>
       </c>
       <c r="P8" t="n">
-        <v>-0.1982</v>
+        <v>-1.3876</v>
       </c>
       <c r="Q8" t="n">
-        <v>-1.9822</v>
+        <v>-2.9733</v>
       </c>
       <c r="R8" t="n">
-        <v>1.784</v>
+        <v>1.5858</v>
       </c>
       <c r="S8" t="n">
-        <v>-1.1193</v>
+        <v>-0.8535</v>
       </c>
       <c r="T8" t="n">
-        <v>-1.0387</v>
+        <v>0.2415</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.0806</v>
+        <v>-1.095</v>
       </c>
       <c r="V8" t="n">
-        <v>0.9405</v>
+        <v>-0.9405</v>
       </c>
       <c r="W8" t="n">
         <v>0.2666</v>
       </c>
       <c r="X8" t="n">
-        <v>0.674</v>
+        <v>-1.2071</v>
       </c>
     </row>
     <row r="9">
@@ -1111,13 +1111,13 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-4.2045</v>
+        <v>-3.9103</v>
       </c>
       <c r="E9" t="n">
-        <v>-1.3445</v>
+        <v>-1.0783</v>
       </c>
       <c r="F9" t="n">
-        <v>-2.86</v>
+        <v>-2.8319</v>
       </c>
       <c r="G9" t="n">
         <v>-1.3198</v>
@@ -1156,13 +1156,13 @@
         <v>0.7929</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.8255</v>
+        <v>-0.5313</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.301</v>
+        <v>-0.0348</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.5246</v>
+        <v>-0.4965</v>
       </c>
       <c r="V9" t="n">
         <v>-1.861</v>
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-8.6357</v>
+        <v>-10.0275</v>
       </c>
       <c r="E10" t="n">
-        <v>-1.9922</v>
+        <v>-3.356</v>
       </c>
       <c r="F10" t="n">
-        <v>-6.6435</v>
+        <v>-6.6716</v>
       </c>
       <c r="G10" t="n">
         <v>0.4757</v>
@@ -1234,13 +1234,13 @@
         <v>1.5858</v>
       </c>
       <c r="S10" t="n">
-        <v>0.9431</v>
+        <v>-0.4488</v>
       </c>
       <c r="T10" t="n">
-        <v>1.9054</v>
+        <v>0.5416</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.9623</v>
+        <v>-0.9903</v>
       </c>
       <c r="V10" t="n">
         <v>-5.6935</v>
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-6.882399999999999</v>
+        <v>-6.584800000000001</v>
       </c>
       <c r="E11" t="n">
-        <v>11.0051</v>
+        <v>11.4714</v>
       </c>
       <c r="F11" t="n">
-        <v>-17.8878</v>
+        <v>-18.0561</v>
       </c>
       <c r="G11" t="n">
         <v>-1.8875</v>
@@ -1312,13 +1312,13 @@
         <v>17.2453</v>
       </c>
       <c r="S11" t="n">
-        <v>-3.973799999999999</v>
+        <v>-3.6761</v>
       </c>
       <c r="T11" t="n">
-        <v>1.4292</v>
+        <v>1.8954</v>
       </c>
       <c r="U11" t="n">
-        <v>-5.403099999999999</v>
+        <v>-5.571399999999999</v>
       </c>
       <c r="V11" t="n">
         <v>-4.3909</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>13.1821</v>
+        <v>11.1316</v>
       </c>
       <c r="E12" t="n">
-        <v>13.7711</v>
+        <v>11.2244</v>
       </c>
       <c r="F12" t="n">
-        <v>-0.589</v>
+        <v>-0.0927</v>
       </c>
       <c r="G12" t="n">
         <v>5.8753</v>
@@ -1390,13 +1390,13 @@
         <v>2.5769</v>
       </c>
       <c r="S12" t="n">
-        <v>3.8905</v>
+        <v>1.84</v>
       </c>
       <c r="T12" t="n">
-        <v>4.6953</v>
+        <v>2.1486</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.8048</v>
+        <v>-0.3085</v>
       </c>
       <c r="V12" t="n">
         <v>2.8216</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>6.292</v>
+        <v>5.3569</v>
       </c>
       <c r="E13" t="n">
-        <v>5.7926</v>
+        <v>5.2833</v>
       </c>
       <c r="F13" t="n">
-        <v>0.4994</v>
+        <v>0.0736</v>
       </c>
       <c r="G13" t="n">
         <v>1.8187</v>
@@ -1468,13 +1468,13 @@
         <v>2.3787</v>
       </c>
       <c r="S13" t="n">
-        <v>2.5328</v>
+        <v>1.5977</v>
       </c>
       <c r="T13" t="n">
-        <v>1.9164</v>
+        <v>1.407</v>
       </c>
       <c r="U13" t="n">
-        <v>0.6163999999999999</v>
+        <v>0.1906</v>
       </c>
       <c r="V13" t="n">
         <v>1.5441</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>3.0274</v>
+        <v>4.0167</v>
       </c>
       <c r="E14" t="n">
-        <v>6.0173</v>
+        <v>6.7304</v>
       </c>
       <c r="F14" t="n">
-        <v>-2.9899</v>
+        <v>-2.7137</v>
       </c>
       <c r="G14" t="n">
         <v>2.8222</v>
@@ -1546,13 +1546,13 @@
         <v>2.1805</v>
       </c>
       <c r="S14" t="n">
-        <v>-0.5966</v>
+        <v>0.3927</v>
       </c>
       <c r="T14" t="n">
-        <v>0.2534</v>
+        <v>0.9665</v>
       </c>
       <c r="U14" t="n">
-        <v>-0.8499</v>
+        <v>-0.5737</v>
       </c>
       <c r="V14" t="n">
         <v>0.6036</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>0.531</v>
+        <v>1.0273</v>
       </c>
       <c r="E15" t="n">
         <v>1.1128</v>
       </c>
       <c r="F15" t="n">
-        <v>-0.5818</v>
+        <v>-0.08550000000000001</v>
       </c>
       <c r="G15" t="n">
         <v>2.9296</v>
@@ -1624,13 +1624,13 @@
         <v>2.3787</v>
       </c>
       <c r="S15" t="n">
-        <v>0.1277</v>
+        <v>0.624</v>
       </c>
       <c r="T15" t="n">
         <v>0.9325</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.8048</v>
+        <v>-0.3085</v>
       </c>
       <c r="V15" t="n">
         <v>-0.9405</v>
@@ -1645,7 +1645,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>L. SIGISMONTI RODRÍGUEZ</t>
+          <t>P. TRUNO SOMS</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,73 +1657,73 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>0.3027</v>
+        <v>0.6425999999999999</v>
       </c>
       <c r="E16" t="n">
-        <v>0.3027</v>
+        <v>-0.1567</v>
       </c>
       <c r="F16" t="n">
-        <v>0</v>
+        <v>0.7994</v>
       </c>
       <c r="G16" t="n">
-        <v>0.3027</v>
+        <v>-3.1723</v>
       </c>
       <c r="H16" t="n">
-        <v>0.3027</v>
+        <v>-0.5704</v>
       </c>
       <c r="I16" t="n">
-        <v>0</v>
+        <v>-2.602</v>
       </c>
       <c r="J16" t="n">
-        <v>0.3027</v>
+        <v>-1.8561</v>
       </c>
       <c r="K16" t="n">
-        <v>0.3027</v>
+        <v>-0.5782</v>
       </c>
       <c r="L16" t="n">
-        <v>0</v>
+        <v>-1.2779</v>
       </c>
       <c r="M16" t="n">
-        <v>0</v>
+        <v>-1.3162</v>
       </c>
       <c r="N16" t="n">
-        <v>0</v>
+        <v>0.0078</v>
       </c>
       <c r="O16" t="n">
-        <v>0</v>
+        <v>-1.3241</v>
       </c>
       <c r="P16" t="n">
-        <v>0</v>
+        <v>-0.1982</v>
       </c>
       <c r="Q16" t="n">
-        <v>0</v>
+        <v>-0.9911</v>
       </c>
       <c r="R16" t="n">
-        <v>0</v>
+        <v>0.7929</v>
       </c>
       <c r="S16" t="n">
-        <v>0</v>
+        <v>0.925</v>
       </c>
       <c r="T16" t="n">
-        <v>0</v>
+        <v>0.2763</v>
       </c>
       <c r="U16" t="n">
-        <v>0</v>
+        <v>0.6487000000000001</v>
       </c>
       <c r="V16" t="n">
-        <v>0</v>
+        <v>3.0882</v>
       </c>
       <c r="W16" t="n">
-        <v>0</v>
+        <v>2.4142</v>
       </c>
       <c r="X16" t="n">
-        <v>0</v>
+        <v>0.674</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>P. TRUNO SOMS</t>
+          <t>L. SIGISMONTI RODRÍGUEZ</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,67 +1735,67 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>-0.3654</v>
+        <v>0.3027</v>
       </c>
       <c r="E17" t="n">
-        <v>-0.8698</v>
+        <v>0.3027</v>
       </c>
       <c r="F17" t="n">
-        <v>0.5044</v>
+        <v>0</v>
       </c>
       <c r="G17" t="n">
-        <v>-3.1723</v>
+        <v>0.3027</v>
       </c>
       <c r="H17" t="n">
-        <v>-0.5704</v>
+        <v>0.3027</v>
       </c>
       <c r="I17" t="n">
-        <v>-2.602</v>
+        <v>0</v>
       </c>
       <c r="J17" t="n">
-        <v>-1.8561</v>
+        <v>0.3027</v>
       </c>
       <c r="K17" t="n">
-        <v>-0.5782</v>
+        <v>0.3027</v>
       </c>
       <c r="L17" t="n">
-        <v>-1.2779</v>
+        <v>0</v>
       </c>
       <c r="M17" t="n">
-        <v>-1.3162</v>
+        <v>0</v>
       </c>
       <c r="N17" t="n">
-        <v>0.0078</v>
+        <v>0</v>
       </c>
       <c r="O17" t="n">
-        <v>-1.3241</v>
+        <v>0</v>
       </c>
       <c r="P17" t="n">
-        <v>-0.1982</v>
+        <v>0</v>
       </c>
       <c r="Q17" t="n">
-        <v>-0.9911</v>
+        <v>0</v>
       </c>
       <c r="R17" t="n">
-        <v>0.7929</v>
+        <v>0</v>
       </c>
       <c r="S17" t="n">
-        <v>-0.083</v>
+        <v>0</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.4368</v>
+        <v>0</v>
       </c>
       <c r="U17" t="n">
-        <v>0.3538</v>
+        <v>0</v>
       </c>
       <c r="V17" t="n">
-        <v>3.0882</v>
+        <v>0</v>
       </c>
       <c r="W17" t="n">
-        <v>2.4142</v>
+        <v>0</v>
       </c>
       <c r="X17" t="n">
-        <v>0.674</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -1813,13 +1813,13 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-2.6913</v>
+        <v>-1.4526</v>
       </c>
       <c r="E18" t="n">
-        <v>2.0786</v>
+        <v>3.0973</v>
       </c>
       <c r="F18" t="n">
-        <v>-4.7699</v>
+        <v>-4.5498</v>
       </c>
       <c r="G18" t="n">
         <v>1.9766</v>
@@ -1858,13 +1858,13 @@
         <v>1.9822</v>
       </c>
       <c r="S18" t="n">
-        <v>-1.3131</v>
+        <v>-0.07439999999999999</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.4881</v>
+        <v>0.5305</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.825</v>
+        <v>-0.6049</v>
       </c>
       <c r="V18" t="n">
         <v>-3.3547</v>
@@ -1891,13 +1891,13 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-2.7706</v>
+        <v>-2.5003</v>
       </c>
       <c r="E19" t="n">
-        <v>-1.4783</v>
+        <v>-1.3765</v>
       </c>
       <c r="F19" t="n">
-        <v>-1.2923</v>
+        <v>-1.1238</v>
       </c>
       <c r="G19" t="n">
         <v>-1.8361</v>
@@ -1936,13 +1936,13 @@
         <v>0.3964</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.5558</v>
+        <v>-0.2854</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.1248</v>
+        <v>-0.0229</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.431</v>
+        <v>-0.2625</v>
       </c>
       <c r="V19" t="n">
         <v>1.2071</v>
@@ -1957,7 +1957,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>D. JUZBASIC</t>
+          <t>P. AVALOS ORTIZ</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,73 +1969,73 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-4.0194</v>
+        <v>-3.7615</v>
       </c>
       <c r="E20" t="n">
-        <v>-3.788</v>
+        <v>-3.0472</v>
       </c>
       <c r="F20" t="n">
-        <v>-0.2315</v>
+        <v>-0.7143</v>
       </c>
       <c r="G20" t="n">
-        <v>-3.3413</v>
+        <v>-4.9156</v>
       </c>
       <c r="H20" t="n">
-        <v>-1.1526</v>
+        <v>-1.03</v>
       </c>
       <c r="I20" t="n">
-        <v>-2.1888</v>
+        <v>-3.8856</v>
       </c>
       <c r="J20" t="n">
-        <v>-1.2237</v>
+        <v>-3.8732</v>
       </c>
       <c r="K20" t="n">
-        <v>-0.625</v>
+        <v>-0.6382</v>
       </c>
       <c r="L20" t="n">
-        <v>-0.5988</v>
+        <v>-3.2349</v>
       </c>
       <c r="M20" t="n">
-        <v>-2.1176</v>
+        <v>-1.0424</v>
       </c>
       <c r="N20" t="n">
-        <v>-0.5276</v>
+        <v>-0.3918</v>
       </c>
       <c r="O20" t="n">
-        <v>-1.59</v>
+        <v>-0.6506</v>
       </c>
       <c r="P20" t="n">
-        <v>-3.568</v>
+        <v>0.7929</v>
       </c>
       <c r="Q20" t="n">
-        <v>-3.9645</v>
+        <v>0</v>
       </c>
       <c r="R20" t="n">
-        <v>0.3964</v>
+        <v>0.7929</v>
       </c>
       <c r="S20" t="n">
-        <v>2.5529</v>
+        <v>1.0352</v>
       </c>
       <c r="T20" t="n">
-        <v>0.7967</v>
+        <v>0.2929</v>
       </c>
       <c r="U20" t="n">
-        <v>1.7563</v>
+        <v>0.7423</v>
       </c>
       <c r="V20" t="n">
-        <v>0.337</v>
+        <v>-0.674</v>
       </c>
       <c r="W20" t="n">
-        <v>0.6036</v>
+        <v>0.5331</v>
       </c>
       <c r="X20" t="n">
-        <v>-0.2666</v>
+        <v>-1.2071</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>P. AVALOS ORTIZ</t>
+          <t>D. JUZBASIC</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,67 +2047,67 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-5.2588</v>
+        <v>-5.1289</v>
       </c>
       <c r="E21" t="n">
-        <v>-3.964</v>
+        <v>-4.1954</v>
       </c>
       <c r="F21" t="n">
-        <v>-1.2948</v>
+        <v>-0.9334</v>
       </c>
       <c r="G21" t="n">
-        <v>-4.9156</v>
+        <v>-3.3413</v>
       </c>
       <c r="H21" t="n">
-        <v>-1.03</v>
+        <v>-1.1526</v>
       </c>
       <c r="I21" t="n">
-        <v>-3.8856</v>
+        <v>-2.1888</v>
       </c>
       <c r="J21" t="n">
-        <v>-3.8732</v>
+        <v>-1.2237</v>
       </c>
       <c r="K21" t="n">
-        <v>-0.6382</v>
+        <v>-0.625</v>
       </c>
       <c r="L21" t="n">
-        <v>-3.2349</v>
+        <v>-0.5988</v>
       </c>
       <c r="M21" t="n">
-        <v>-1.0424</v>
+        <v>-2.1176</v>
       </c>
       <c r="N21" t="n">
-        <v>-0.3918</v>
+        <v>-0.5276</v>
       </c>
       <c r="O21" t="n">
-        <v>-0.6506</v>
+        <v>-1.59</v>
       </c>
       <c r="P21" t="n">
-        <v>0.7929</v>
+        <v>-3.568</v>
       </c>
       <c r="Q21" t="n">
-        <v>0</v>
+        <v>-3.9645</v>
       </c>
       <c r="R21" t="n">
-        <v>0.7929</v>
+        <v>0.3964</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.4622</v>
+        <v>1.4435</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.624</v>
+        <v>0.3892</v>
       </c>
       <c r="U21" t="n">
-        <v>0.1618</v>
+        <v>1.0543</v>
       </c>
       <c r="V21" t="n">
-        <v>-0.674</v>
+        <v>0.337</v>
       </c>
       <c r="W21" t="n">
-        <v>0.5331</v>
+        <v>0.6036</v>
       </c>
       <c r="X21" t="n">
-        <v>-1.2071</v>
+        <v>-0.2666</v>
       </c>
     </row>
     <row r="22">
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>8.229699999999998</v>
+        <v>9.634500000000003</v>
       </c>
       <c r="E22" t="n">
-        <v>18.975</v>
+        <v>18.9751</v>
       </c>
       <c r="F22" t="n">
-        <v>-10.7454</v>
+        <v>-9.340200000000001</v>
       </c>
       <c r="G22" t="n">
         <v>2.459799999999999</v>
@@ -2149,7 +2149,7 @@
         <v>16.0441</v>
       </c>
       <c r="L22" t="n">
-        <v>4.526</v>
+        <v>4.526000000000001</v>
       </c>
       <c r="M22" t="n">
         <v>-18.1101</v>
@@ -2170,13 +2170,13 @@
         <v>13.8756</v>
       </c>
       <c r="S22" t="n">
-        <v>6.0932</v>
+        <v>7.4983</v>
       </c>
       <c r="T22" t="n">
-        <v>6.920599999999999</v>
+        <v>6.9206</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.8272000000000004</v>
+        <v>0.5778000000000001</v>
       </c>
       <c r="V22" t="n">
         <v>4.6324</v>
